--- a/chapters/collection/clickstream_logs.xlsx
+++ b/chapters/collection/clickstream_logs.xlsx
@@ -1900,7 +1900,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notes for the analyst</t>
+          <t>Notes for the analyst (a realistic teaching dataset written for the book)</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>One row per event; you only capture events you INSTRUMENTED — untagged actions are invisible (missing by design).</t>
+          <t>One row per event; you only capture events you INSTRUMENTED, and untagged actions are invisible (missing by design).</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clean before analysis: drop is_bot=1, and remember this is NOT a designed sample — it reflects whoever used the product.</t>
+          <t>Clean before analysis: drop is_bot=1, and remember this is NOT a designed sample, since it reflects whoever used the product.</t>
         </is>
       </c>
     </row>
